--- a/tame_output/ON/bt/strategyON_20240220.xlsx
+++ b/tame_output/ON/bt/strategyON_20240220.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.9%</t>
+          <t>131.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>1.556028962135045</v>
+        <v>1.556524594042884</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.763964250958382</v>
+        <v>3.764162503721517</v>
       </c>
       <c r="F1879" t="n">
-        <v>2.37785137696817</v>
+        <v>2.378835186847865</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.568619916599014</v>
+        <v>4.56921020252683</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240220.xlsx
+++ b/tame_output/ON/bt/strategyON_20240220.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>1.556524594042884</v>
+        <v>1.556203716008778</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.764162503721517</v>
+        <v>3.764034152507875</v>
       </c>
       <c r="F1879" t="n">
-        <v>2.378835186847865</v>
+        <v>2.378285004644926</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.56921020252683</v>
+        <v>4.568880093205067</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240220.xlsx
+++ b/tame_output/ON/bt/strategyON_20240220.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.0%</t>
+          <t>449.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-2.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.0%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>1.556203716008778</v>
+        <v>1.50093788616164</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.764034152507875</v>
+        <v>3.741927820569019</v>
       </c>
       <c r="F1879" t="n">
-        <v>2.378285004644926</v>
+        <v>2.305275999819241</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.568880093205067</v>
+        <v>4.525074690309656</v>
       </c>
     </row>
   </sheetData>
